--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -776,27 +812,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>SEGUNDA - AVES 24/11/25</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="8" t="n">
         <v>105840</v>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>COXINHA DA ASA DE FRANGO KG</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
-        <v>13.99</v>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="10" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="15">
@@ -1256,27 +1292,27 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>SEGUNDA - AVES 24/11/25</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
-        <v>105770</v>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="n">
-        <v>11.69</v>
+      <c r="C34" s="8" t="n">
+        <v>228422</v>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="10" t="n">
+        <v>17.99</v>
       </c>
     </row>
     <row r="35">
@@ -1291,40 +1327,40 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>132881</v>
+        <v>105770</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>SALSICHA FRIATO KG</t>
+          <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="n">
-        <v>8.99</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SEGUNDA - PERECIVEIS 24/11/25</t>
+          <t>SEGUNDA - AVES 24/11/25</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>170464</v>
+        <v>132881</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+          <t>SALSICHA FRIATO KG</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="n">
-        <v>2.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="37">
@@ -1339,19 +1375,43 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
+        <v>170464</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="6" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 24/11/25</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>138538</v>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>TEKITOS SEARA 300G</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>FRANGO, QUEIJO COM OREGANO</t>
         </is>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>8.59</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2264,27 +2300,27 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>SEGUNDA - AVES 15/12/25</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
-      <c r="C77" s="3" t="n">
+      <c r="C77" s="8" t="n">
         <v>119927</v>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr"/>
-      <c r="F77" s="6" t="n">
-        <v>9.99</v>
+      <c r="E77" s="9" t="inlineStr"/>
+      <c r="F77" s="10" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="78">
@@ -2720,27 +2756,27 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>SEGUNDA - AVES 15/12/25</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
         </is>
       </c>
-      <c r="C96" s="3" t="n">
+      <c r="C96" s="8" t="n">
         <v>132881</v>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>SALSICHA FRIATO KG</t>
         </is>
       </c>
-      <c r="E96" s="5" t="inlineStr"/>
-      <c r="F96" s="6" t="n">
-        <v>8.99</v>
+      <c r="E96" s="9" t="inlineStr"/>
+      <c r="F96" s="10" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="97">

--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988B9A53-60EF-4C84-AB7F-7E945B23E545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B26F7F8-F933-445C-8D3A-9DBE62736CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="54">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -114,12 +109,51 @@
     <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
   </si>
   <si>
+    <t>SEGUNDA - AÇOUGUE 19/01/25</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>ACEM BOVINO KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CAPA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>COXÃO MOLE KG</t>
+  </si>
+  <si>
+    <t>PATINHO BOVINO KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA CARRE KG</t>
+  </si>
+  <si>
+    <t>BISTECA SUINA DO PERNIL KG</t>
+  </si>
+  <si>
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
     <t>LINGUICA TIPO CALABRESA SADIA KG</t>
   </si>
   <si>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
+  </si>
+  <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
   </si>
   <si>
@@ -144,7 +178,10 @@
     <t>FRANGO, QUEIJO COM OREGANO</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>#10 OVOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OVOS DE GRANJA IANA BDJ 30UN BRANCOS </t>
   </si>
 </sst>
 </file>
@@ -154,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,8 +227,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -202,6 +257,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -232,7 +293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -249,6 +310,15 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -256,6 +326,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -561,18 +634,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="46" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -588,11 +661,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -606,11 +679,11 @@
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="F2" s="10">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -624,11 +697,11 @@
         <v>11</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="F4" s="10">
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -642,11 +715,11 @@
         <v>13</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="F5" s="10">
         <v>21.99</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -660,11 +733,11 @@
         <v>15</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="F6" s="10">
         <v>6.79</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -678,11 +751,11 @@
         <v>17</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="F7" s="10">
         <v>10.99</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -696,11 +769,11 @@
         <v>19</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="F9" s="10">
         <v>13.99</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -714,11 +787,11 @@
         <v>20</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="F10" s="10">
         <v>9.99</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -732,14 +805,11 @@
         <v>21</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <v>13.99</v>
       </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -753,11 +823,11 @@
         <v>22</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="F12" s="10">
         <v>13.99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>9</v>
       </c>
@@ -771,11 +841,11 @@
         <v>23</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -789,11 +859,11 @@
         <v>24</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -807,11 +877,11 @@
         <v>25</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="F15" s="10">
         <v>9.99</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -825,7 +895,7 @@
         <v>26</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="F16" s="10">
         <v>10.99</v>
       </c>
     </row>
@@ -843,7 +913,7 @@
         <v>27</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="F17" s="10">
         <v>12.99</v>
       </c>
     </row>
@@ -861,141 +931,339 @@
         <v>28</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="F18" s="10">
         <v>14.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="7">
+        <v>105470</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="12">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="7">
+        <v>105461</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="12">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="7">
+        <v>239334</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="12">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="7">
+        <v>105468</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="7">
+        <v>105471</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="12">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="7">
+        <v>105435</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="12">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="7">
+        <v>105452</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="12">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="7">
+        <v>106053</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="7">
+        <v>105062</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="8"/>
+      <c r="F27" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3">
+        <v>105713</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="10">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
-        <v>105713</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B29" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="7">
+        <v>305039</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="8"/>
+      <c r="F29" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="3">
+        <v>228422</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="10">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="3">
+        <v>272499</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="10">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="3">
+        <v>292399</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="10">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="3">
+        <v>132881</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="10">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="3">
+        <v>170464</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="10">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="3">
+        <v>138538</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F35" s="10">
+        <v>9.39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
-        <v>228422</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" s="3">
-        <v>272499</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="3">
-        <v>292399</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
-        <v>11.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="3">
-        <v>132881</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="3">
-        <v>170464</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="3">
-        <v>138538</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="7">
-        <v>9.39</v>
+      <c r="B37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="7">
+        <v>328966</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="12">
+        <v>14.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3585D5D7-DEC4-4731-B20B-90DA70D1FA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C916AC5E-E480-4FFE-8283-422EECB9424B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -182,9 +177,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +215,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,6 +245,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -262,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -279,13 +298,21 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,18 +615,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -618,7 +642,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -636,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>11.99</v>
       </c>
     </row>
@@ -654,7 +678,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>15.99</v>
       </c>
     </row>
@@ -672,26 +696,26 @@
         <v>12</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>11.99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="8">
         <v>105842</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
-        <v>13.99</v>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10">
+        <v>14.99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -708,7 +732,7 @@
         <v>16</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>28.99</v>
       </c>
     </row>
@@ -726,7 +750,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>9.99</v>
       </c>
     </row>
@@ -744,7 +768,7 @@
         <v>18</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>13.99</v>
       </c>
     </row>
@@ -762,26 +786,26 @@
         <v>19</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>13.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="8">
         <v>109597</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
-        <v>16.989999999999998</v>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -798,7 +822,7 @@
         <v>21</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>10.99</v>
       </c>
     </row>
@@ -816,7 +840,7 @@
         <v>22</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <v>9.99</v>
       </c>
     </row>
@@ -834,7 +858,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>23.99</v>
       </c>
     </row>
@@ -852,7 +876,7 @@
         <v>24</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -870,7 +894,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -888,7 +912,7 @@
         <v>26</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>14.99</v>
       </c>
     </row>
@@ -906,7 +930,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>13.99</v>
       </c>
     </row>
@@ -924,7 +948,7 @@
         <v>30</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>23.99</v>
       </c>
     </row>
@@ -942,7 +966,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <v>34.99</v>
       </c>
     </row>
@@ -960,7 +984,7 @@
         <v>32</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -978,7 +1002,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <v>39.99</v>
       </c>
     </row>
@@ -996,7 +1020,7 @@
         <v>34</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <v>34.99</v>
       </c>
     </row>
@@ -1014,7 +1038,7 @@
         <v>35</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>11.99</v>
       </c>
     </row>
@@ -1032,7 +1056,7 @@
         <v>37</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -1050,7 +1074,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -1068,7 +1092,7 @@
         <v>39</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <v>12.99</v>
       </c>
     </row>
@@ -1086,7 +1110,7 @@
         <v>41</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -1104,7 +1128,7 @@
         <v>42</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="F29" s="6">
         <v>8.99</v>
       </c>
     </row>
@@ -1122,7 +1146,7 @@
         <v>43</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>6.99</v>
       </c>
     </row>
@@ -1140,7 +1164,7 @@
         <v>44</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <v>11.99</v>
       </c>
     </row>
@@ -1158,7 +1182,7 @@
         <v>45</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>7.99</v>
       </c>
     </row>
@@ -1176,7 +1200,7 @@
         <v>47</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <v>2.29</v>
       </c>
     </row>
@@ -1196,15 +1220,11 @@
       <c r="E34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C9A002-50B2-4C8E-987A-32FE17A2770C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D171DC4-5815-440F-8481-648956DFFDBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -67,7 +67,7 @@
     <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
   </si>
   <si>
-    <t>SEGUNDA - COROCOCO 15/02/26</t>
+    <t>SEGUNDA - COROCOCO 16/02/26</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #01 AVES</t>
@@ -97,7 +97,49 @@
     <t>PEITO DE FRANGO AMERICANO BDJ 1KG</t>
   </si>
   <si>
+    <t>SEGUNDA - AÇOUGUE 16/02/26</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>ACEM BOVINO KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA SERENADA KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>COXÃO MOLE KG</t>
+  </si>
+  <si>
+    <t>MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>SUINO CAIPIRA KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>SUAN SUINA KG</t>
+  </si>
+  <si>
+    <t>TOUCINHO FRESCO KG</t>
+  </si>
+  <si>
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+  </si>
+  <si>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
@@ -125,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +203,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +233,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -203,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -220,6 +286,15 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -227,6 +302,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,15 +607,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="12" style="8" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -556,7 +637,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -574,7 +655,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="F2" s="10">
         <v>11.99</v>
       </c>
     </row>
@@ -592,7 +673,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="F3" s="10">
         <v>3.49</v>
       </c>
     </row>
@@ -610,7 +691,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="F4" s="10">
         <v>15.99</v>
       </c>
     </row>
@@ -628,7 +709,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="F5" s="10">
         <v>5.99</v>
       </c>
     </row>
@@ -646,7 +727,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="F7" s="10">
         <v>14.99</v>
       </c>
     </row>
@@ -664,7 +745,7 @@
         <v>18</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="F8" s="10">
         <v>28.99</v>
       </c>
     </row>
@@ -682,7 +763,7 @@
         <v>19</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="F9" s="10">
         <v>9.99</v>
       </c>
     </row>
@@ -700,7 +781,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="F10" s="10">
         <v>13.99</v>
       </c>
     </row>
@@ -718,7 +799,7 @@
         <v>21</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="F11" s="10">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -736,7 +817,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="F12" s="10">
         <v>10.99</v>
       </c>
     </row>
@@ -754,7 +835,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="F13" s="10">
         <v>9.99</v>
       </c>
     </row>
@@ -772,85 +853,284 @@
         <v>24</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="F14" s="10">
         <v>17.989999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="7">
+        <v>105470</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="8"/>
+      <c r="F15" s="12">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="7">
+        <v>105459</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="8"/>
+      <c r="F16" s="12">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="7">
+        <v>105461</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="8"/>
+      <c r="F17" s="12">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="7">
+        <v>105457</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="12">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="7">
+        <v>105458</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="8"/>
+      <c r="F19" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="7">
+        <v>105435</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="12">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="7">
+        <v>107260</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="12">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="7">
+        <v>298422</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="12">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="7">
+        <v>106034</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="12">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="7">
+        <v>106032</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="7">
+        <v>305039</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="8"/>
+      <c r="F25" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="3">
         <v>228422</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="D26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="10">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="3">
         <v>330507</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="D27" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="10">
         <v>8.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="3">
         <v>227341</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="D28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="10">
         <v>7.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="3">
         <v>138538</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="7">
+      <c r="D29" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29" s="10">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72188B44-922A-485F-8D37-52E30EC9A4B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6314B973-39C8-4EC8-81FE-27D4AA02E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,38 +212,43 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -293,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -301,34 +306,47 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -631,645 +649,648 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="77.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29" style="17" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>100038</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="10">
+      <c r="E2" s="15"/>
+      <c r="F2" s="8">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="9">
         <v>193650</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="11">
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="9">
         <v>336608</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="11">
         <v>11.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="9">
         <v>304952</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="16"/>
       <c r="F6" s="11">
         <v>20.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="9">
         <v>276943</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="11">
         <v>15.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="9">
         <v>302944</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="11">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>105842</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="10">
+      <c r="E10" s="15"/>
+      <c r="F10" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="9">
         <v>294636</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="16"/>
       <c r="F11" s="11">
         <v>26.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>105838</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="10">
+      <c r="E12" s="15"/>
+      <c r="F12" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="s">
+    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="9">
         <v>111565</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="16"/>
       <c r="F13" s="11">
         <v>13.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>105840</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="10">
+      <c r="E14" s="15"/>
+      <c r="F14" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="9">
         <v>108785</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="16"/>
       <c r="F15" s="11">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="5" t="s">
+    <row r="16" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="9">
         <v>284816</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="16"/>
       <c r="F16" s="11">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="9">
         <v>109597</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="11">
         <v>17.489999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="9">
         <v>119927</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="11">
         <v>10.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="5" t="s">
+    <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="9">
         <v>185934</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="16"/>
       <c r="F19" s="11">
         <v>10.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="5" t="s">
+    <row r="20" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="9">
         <v>195365</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="11">
         <v>15.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="5" t="s">
+    <row r="21" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="9">
         <v>247629</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="11">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="9">
         <v>105470</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="11">
         <v>23.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="9">
         <v>105461</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="16"/>
       <c r="F23" s="11">
         <v>33.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="9">
         <v>105456</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="11">
         <v>28.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="9">
         <v>105471</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="11">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="9">
         <v>105449</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="11">
         <v>34.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="9">
         <v>105435</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="8"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="11">
         <v>38.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="9">
         <v>105062</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="8"/>
+      <c r="E28" s="16"/>
       <c r="F28" s="11">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="9">
         <v>106008</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="8"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="11">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+    <row r="30" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="9">
         <v>106032</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="8"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="11">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="5" t="s">
+    <row r="31" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="9">
         <v>295493</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="8"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="11">
         <v>11.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+    <row r="32" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="9">
         <v>305039</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="8"/>
+      <c r="E32" s="16"/>
       <c r="F32" s="11">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+    <row r="33" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="9">
         <v>228422</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="16"/>
       <c r="F33" s="11">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="5" t="s">
+    <row r="34" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="9">
         <v>330507</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="8"/>
+      <c r="E34" s="16"/>
       <c r="F34" s="11">
         <v>8.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="5" t="s">
+    <row r="35" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="9">
         <v>105770</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E35" s="8"/>
+      <c r="E35" s="16"/>
       <c r="F35" s="11">
         <v>11.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="9">
         <v>227341</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="8"/>
+      <c r="E36" s="16"/>
       <c r="F36" s="11">
         <v>7.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="5" t="s">
+    <row r="37" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="9">
         <v>138538</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F37" s="11">
@@ -1277,6 +1298,10 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6314B973-39C8-4EC8-81FE-27D4AA02E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C582E20F-AF03-48C3-8C81-F5B2B168BBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,13 +40,13 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SEGUNDA - COROCOCO 23/02/26</t>
+    <t>TERÇA - AÇOUGUE 24/02/26</t>
   </si>
   <si>
     <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
   </si>
   <si>
-    <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+    <t>ARROZ REI ARTHUR PCT 5KG TIPO 1 BRANCO</t>
   </si>
   <si>
     <t>SEGUNDA - PERECIVEIS 23/02/26</t>
@@ -82,33 +82,15 @@
     <t>#06 AÇOUGUE - #01 AVES</t>
   </si>
   <si>
-    <t>ASA DE FRANGO KG</t>
-  </si>
-  <si>
     <t>CORAÇÃO DE FRANGO AVISPARA BDJ 1KG</t>
   </si>
   <si>
-    <t>COXA COM SOBRECOXA DE FRANGO KG</t>
-  </si>
-  <si>
     <t>COXA DE FRANGO SADIA BDJ 1KG</t>
   </si>
   <si>
-    <t>COXINHA DA ASA DE FRANGO KG</t>
-  </si>
-  <si>
     <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
   </si>
   <si>
-    <t xml:space="preserve">COXINHA EMPANADA CEARA 400G APIMENTADA </t>
-  </si>
-  <si>
-    <t>FILÉ DE PEITO DE FRANGO KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRANGO AMERICANO KG CONGELADO </t>
-  </si>
-  <si>
     <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
   </si>
   <si>
@@ -118,37 +100,34 @@
     <t>PEITO DE FRANGO AMERICANO BDJ 1KG</t>
   </si>
   <si>
-    <t>SEGUNDA - AÇOUGUE 23/02/25</t>
-  </si>
-  <si>
     <t>#06 AÇOUGUE - #02 BOVINA</t>
   </si>
   <si>
-    <t>ACEM BOVINO KG</t>
+    <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DA PALETA KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DO ACÉM KG</t>
   </si>
   <si>
     <t>BISTECA BOVINA DO CONTRA FILE KG</t>
   </si>
   <si>
-    <t>CARNE DE SOL KG SEGUNDA</t>
-  </si>
-  <si>
-    <t>COSTELA BOVINA KG</t>
-  </si>
-  <si>
-    <t>COXÃO DURO KG</t>
-  </si>
-  <si>
-    <t>COXÃO MOLE KG</t>
+    <t>CARNE BOVINA SERENADA KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>PATINHO BOVINO KG</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #03 SUÍNA</t>
   </si>
   <si>
-    <t>BISTECA SUINA DO PERNIL KG</t>
-  </si>
-  <si>
-    <t>INGREDIENTES PARA FEIJOADA KG</t>
+    <t>BISTECA SUINA CARRE KG</t>
   </si>
   <si>
     <t>TOUCINHO FRESCO KG</t>
@@ -163,18 +142,12 @@
     <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
-    <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
-  </si>
-  <si>
     <t>LINGUIÇA NUTRIBRAS 350G CALABRESA</t>
   </si>
   <si>
     <t xml:space="preserve">MORTADELA PERDIGÃO KG FRANGO </t>
   </si>
   <si>
-    <t>SALSICHA AMERICANO KG PARA HOT DOG</t>
-  </si>
-  <si>
     <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
   </si>
   <si>
@@ -182,6 +155,9 @@
   </si>
   <si>
     <t>FRANGO, QUEIJO COM OREGANO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COXINHA EMPANADA SEARA 400G APIMENTADA </t>
   </si>
 </sst>
 </file>
@@ -218,37 +194,37 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -298,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -312,40 +288,31 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,18 +619,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultRowHeight="34.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="77.140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29" style="17" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,632 +643,503 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6">
-        <v>100038</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="C2" s="5">
+        <v>100031</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="8">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E2" s="6"/>
+      <c r="F2" s="12">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>193650</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="11">
+      <c r="E4" s="10"/>
+      <c r="F4" s="14">
         <v>9.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>336608</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="11">
+      <c r="E5" s="10"/>
+      <c r="F5" s="14">
         <v>11.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>304952</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="11">
+      <c r="E6" s="10"/>
+      <c r="F6" s="14">
         <v>20.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>276943</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="11">
+      <c r="E7" s="10"/>
+      <c r="F7" s="14">
         <v>15.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>302944</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="11">
+      <c r="E8" s="10"/>
+      <c r="F8" s="14">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
-        <v>105842</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="8">
+        <v>294636</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="8">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="10"/>
+      <c r="F10" s="14">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="9">
-        <v>294636</v>
-      </c>
-      <c r="D11" s="10" t="s">
+      <c r="C11" s="8">
+        <v>111565</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="11">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+      <c r="E11" s="10"/>
+      <c r="F11" s="14">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="6">
-        <v>105838</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="C12" s="8">
+        <v>108785</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="8">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="10"/>
+      <c r="F12" s="14">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="9">
-        <v>111565</v>
-      </c>
-      <c r="D13" s="10" t="s">
+      <c r="C13" s="8">
+        <v>284816</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="8">
+        <v>185934</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="11">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="6">
-        <v>105840</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="8">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="10"/>
+      <c r="F14" s="14">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="9">
-        <v>108785</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="11">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="8">
+        <v>195365</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="14">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="9">
-        <v>284816</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="8">
+        <v>247629</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="14">
+        <v>17.989999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="C17" s="5">
+        <v>105459</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="12">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="9">
-        <v>109597</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="11">
-        <v>17.489999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="5">
+        <v>105460</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="12">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="9">
-        <v>119927</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="11">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="9">
-        <v>185934</v>
-      </c>
-      <c r="D19" s="10" t="s">
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="5">
+        <v>158997</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="11">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E19" s="6"/>
+      <c r="F19" s="12">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="9">
-        <v>195365</v>
-      </c>
-      <c r="D20" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="8">
+        <v>105461</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="11">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="9">
-        <v>247629</v>
-      </c>
-      <c r="D21" s="10" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="14">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="5">
+        <v>105457</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="11">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="E21" s="6"/>
+      <c r="F21" s="12">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5">
+        <v>105458</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="E22" s="6"/>
+      <c r="F22" s="12">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="5">
+        <v>105452</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="9">
-        <v>105470</v>
-      </c>
-      <c r="D22" s="10" t="s">
+      <c r="E23" s="6"/>
+      <c r="F23" s="12">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="11">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="9">
-        <v>105461</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="C24" s="5">
+        <v>106053</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="11">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="9">
-        <v>105456</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="6"/>
+      <c r="F24" s="12">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="8">
+        <v>106032</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="11">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="9">
-        <v>105471</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10"/>
+      <c r="F25" s="14">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="11">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="9">
-        <v>105449</v>
-      </c>
-      <c r="D26" s="10" t="s">
+      <c r="C26" s="8">
+        <v>295493</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="11">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="9">
-        <v>105435</v>
-      </c>
-      <c r="D27" s="10" t="s">
+      <c r="E26" s="10"/>
+      <c r="F26" s="14">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="5">
+        <v>305039</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="11">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E27" s="6"/>
+      <c r="F27" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="8">
+        <v>330507</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="9">
-        <v>105062</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="10"/>
+      <c r="F28" s="14">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="8">
+        <v>105770</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="11">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="9">
-        <v>106008</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="10"/>
+      <c r="F29" s="14">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="11">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="9">
-        <v>106032</v>
-      </c>
-      <c r="D30" s="10" t="s">
+      <c r="C30" s="8">
+        <v>138538</v>
+      </c>
+      <c r="D30" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="11">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="3" t="s">
+      <c r="E30" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="9">
-        <v>295493</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="11">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="9">
-        <v>305039</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="F32" s="11">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C33" s="9">
-        <v>228422</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="11">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="9">
-        <v>330507</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="F34" s="11">
+      <c r="F30" s="14">
         <v>8.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C35" s="9">
-        <v>105770</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="11">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="9">
-        <v>227341</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="11">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="9">
-        <v>138538</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F37" s="11">
-        <v>8.99</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="95" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406BC053-0E2F-42E6-AB73-B68371A161E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069E3D91-0A77-4DA9-A52C-EC7CF64FB958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,51 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
+    <t>SEGUNDA/TERÇA - PEECIVEIS 23 E 24/03/26</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+  </si>
+  <si>
+    <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
+  </si>
+  <si>
+    <t>PIZZA REZENDE 400G FRANGO COM REQUEIJÃO</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
+  </si>
+  <si>
+    <t>BEBIDA LACTEA FRUTILAC BDJ 480G MORANGO</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+  </si>
+  <si>
+    <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - MASSAS</t>
+  </si>
+  <si>
+    <t>CAPELETTI MEZZANI 400G</t>
+  </si>
+  <si>
+    <t>4 QUEIJOS, CARNE, FRANGO</t>
+  </si>
+  <si>
+    <t>RAVIOLI MEZZANI 400G</t>
+  </si>
+  <si>
+    <t>TAGLIATELLE FRESCO MEZZANI 500G</t>
+  </si>
+  <si>
+    <t>TALHARIM FRESCO MEZZANI 500G</t>
+  </si>
+  <si>
     <t>SEGUNDA - COROCOCO 23/03/26</t>
   </si>
   <si>
@@ -49,6 +94,9 @@
     <t>ASA DE FRANGO KG</t>
   </si>
   <si>
+    <t>CORAÇÃO DE FRANGO AVISPARA BDJ 1KG</t>
+  </si>
+  <si>
     <t>COXA COM SOBRECOXA DE FRANGO KG</t>
   </si>
   <si>
@@ -70,70 +118,22 @@
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
+    <t>LINGUIÇA CALABRESA SADIA 400G DEFUMADA</t>
+  </si>
+  <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
   </si>
   <si>
     <t>LINGUIÇA SUINA PERDIGÃO KG</t>
   </si>
   <si>
+    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
+  </si>
+  <si>
+    <t>MORTADELA PERDIGÃO MISTA 1KG</t>
+  </si>
+  <si>
     <t>SALSICHA FRIATO KG</t>
-  </si>
-  <si>
-    <t>SEGUNDA/TERÇA - PEECIVEIS 23 E 24/03/26</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
-  </si>
-  <si>
-    <t>BATATAS CONGELADAS SADIA PCT 400G PALITO PRE-FRITA</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
-  </si>
-  <si>
-    <t>PIZZA REZENDE 400G FRANGO COM REQUEIJÃO</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
-  </si>
-  <si>
-    <t>BEBIDA LACTEA FRUTILAC BDJ 480G MORANGO</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
-  </si>
-  <si>
-    <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - MASSAS</t>
-  </si>
-  <si>
-    <t>CAPELETTI MEZZANI 400G</t>
-  </si>
-  <si>
-    <t>4 QUEIJOS, CARNE, FRANGO</t>
-  </si>
-  <si>
-    <t>RAVIOLI MEZZANI 400G</t>
-  </si>
-  <si>
-    <t>TAGLIATELLE FRESCO MEZZANI 500G</t>
-  </si>
-  <si>
-    <t>TALHARIM FRESCO MEZZANI 500G</t>
-  </si>
-  <si>
-    <t>CORAÇÃO DE FRANGO AVISPARA BDJ 1KG</t>
-  </si>
-  <si>
-    <t>LINGUIÇA CALABRESA SADIA 400G DEFUMADA</t>
-  </si>
-  <si>
-    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
-  </si>
-  <si>
-    <t>MORTADELA PERDIGÃO MISTA 1KG</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
@@ -559,10 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
@@ -601,14 +598,14 @@
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>105842</v>
+        <v>227503</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="7">
-        <v>13.49</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -616,17 +613,17 @@
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>105838</v>
+        <v>322605</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="7">
-        <v>8.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -634,17 +631,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>105840</v>
+        <v>306946</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="7">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -652,17 +649,17 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3">
-        <v>109597</v>
+        <v>302944</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="7">
-        <v>17.989999999999998</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -670,17 +667,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
-        <v>119927</v>
+        <v>113525</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F6" s="7">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -688,17 +687,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3">
-        <v>225767</v>
+        <v>203414</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F7" s="7">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -706,17 +707,17 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3">
-        <v>185934</v>
+        <v>206159</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="7">
-        <v>10.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -727,312 +728,307 @@
         <v>15</v>
       </c>
       <c r="C9" s="3">
-        <v>228422</v>
+        <v>109759</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3">
-        <v>146785</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>26.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
-        <v>132881</v>
+        <v>105842</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="7">
-        <v>7.99</v>
+        <v>13.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="3">
+        <v>294636</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>25.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3">
-        <v>227503</v>
+        <v>105838</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="7">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="C14" s="3">
-        <v>322605</v>
+        <v>105840</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="7">
-        <v>17.989999999999998</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3">
-        <v>306946</v>
+        <v>109597</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="7">
-        <v>4.99</v>
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3">
-        <v>302944</v>
+        <v>119927</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="7">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3">
-        <v>113525</v>
+        <v>225767</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>30</v>
-      </c>
+      <c r="E17" s="5"/>
       <c r="F17" s="7">
-        <v>15.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3">
-        <v>203414</v>
+        <v>185934</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="7">
-        <v>15.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3">
-        <v>206159</v>
+        <v>304309</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="7">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C20" s="3">
-        <v>109759</v>
+        <v>228422</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="7">
-        <v>13.99</v>
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="3">
+        <v>146785</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>26.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="C22" s="3">
-        <v>294636</v>
+        <v>292399</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="7">
-        <v>25.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C23" s="3">
-        <v>304309</v>
+        <v>119916</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="7">
-        <v>8.99</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3">
-        <v>292399</v>
+        <v>132881</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="7">
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C25" s="3">
-        <v>119916</v>
+        <v>170464</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="7">
-        <v>11.49</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="3">
-        <v>170464</v>
+        <v>138538</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="5"/>
+        <v>40</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="F26" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="3">
-        <v>138538</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="7">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{069E3D91-0A77-4DA9-A52C-EC7CF64FB958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30777DC1-EBD4-44B4-BE7D-31F7EDE9451E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="54">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -115,10 +115,46 @@
     <t xml:space="preserve">GALINHA NOROESTE KG CONGELADA </t>
   </si>
   <si>
+    <t>SEGUNDA - AÇOUGUE 23/03/26</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>ACEM BOVINO COM OSSO KG</t>
+  </si>
+  <si>
+    <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>CARNE BOVINA SERENADA KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>COSTELA SUINA KG</t>
+  </si>
+  <si>
+    <t>PELE SUINA KG</t>
+  </si>
+  <si>
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
   </si>
   <si>
     <t>LINGUIÇA CALABRESA SADIA 400G DEFUMADA</t>
+  </si>
+  <si>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
@@ -155,7 +191,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,21 +211,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -233,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -241,22 +287,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,476 +615,646 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="39" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>227503</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="11"/>
+      <c r="F2" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>322605</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="11"/>
+      <c r="F3" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>306946</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="11"/>
+      <c r="F4" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>302944</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="11"/>
+      <c r="F5" s="8">
         <v>5.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>113525</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>203414</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>206159</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="11"/>
+      <c r="F8" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>109759</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="11"/>
+      <c r="F9" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>105842</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="11"/>
+      <c r="F11" s="8">
         <v>13.49</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>294636</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="11"/>
+      <c r="F12" s="8">
         <v>25.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>105838</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="11"/>
+      <c r="F13" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>105840</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="11"/>
+      <c r="F14" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>109597</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="11"/>
+      <c r="F15" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>119927</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="11"/>
+      <c r="F16" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>225767</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="11"/>
+      <c r="F17" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>185934</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="11"/>
+      <c r="F18" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="6">
+        <v>157014</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="8">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="3">
+      <c r="B20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="6">
+        <v>105459</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="8">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="6">
+        <v>105457</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="8">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" s="6">
+        <v>105458</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="8">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="6">
+        <v>105471</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="8">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="6">
+        <v>107260</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="8">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="6">
+        <v>105433</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="8">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="6">
+        <v>106052</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="6">
         <v>304309</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="D27" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="28" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="6">
+        <v>305039</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="8">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="3">
+      <c r="B29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="6">
         <v>228422</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="D29" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="30" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="3">
+      <c r="B30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="6">
         <v>146785</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="D30" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="11"/>
+      <c r="F30" s="8">
         <v>26.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" s="3">
+    <row r="31" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="6">
         <v>292399</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="D31" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="3">
+    <row r="32" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="6">
         <v>119916</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="D32" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="8">
         <v>11.49</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+    <row r="33" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="3">
+      <c r="B33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="6">
         <v>132881</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="D33" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="11"/>
+      <c r="F33" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="3">
+    <row r="34" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="6">
         <v>170464</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="D34" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="11"/>
+      <c r="F34" s="8">
         <v>2.19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="3">
+    <row r="35" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="6">
         <v>138538</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="7">
+      <c r="D35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="8">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9874DEDB-5446-41F6-BBF6-CB3F2945ABC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9D6277-165C-4906-B77E-2A4744DA9B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -190,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,24 +205,47 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -238,6 +256,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -268,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -276,22 +300,47 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,635 +647,635 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultColWidth="44.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" style="17" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>227503</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="15"/>
+      <c r="F2" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>320013</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="15"/>
+      <c r="F3" s="8">
         <v>2.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>276943</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="15"/>
+      <c r="F4" s="8">
         <v>15.59</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>302944</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="15"/>
+      <c r="F5" s="8">
         <v>5.89</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>105842</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="15"/>
+      <c r="F7" s="8">
         <v>13.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>294636</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="15"/>
+      <c r="F8" s="8">
         <v>26.59</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>105838</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="15"/>
+      <c r="F9" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>104602</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="15"/>
+      <c r="F10" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="9">
         <v>105840</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="16"/>
+      <c r="F11" s="11">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>338685</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="15"/>
+      <c r="F12" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="9">
         <v>109597</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E13" s="16"/>
+      <c r="F13" s="11">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>119927</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="15"/>
+      <c r="F14" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>225767</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="15"/>
+      <c r="F15" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>195365</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="15"/>
+      <c r="F16" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>224723</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="15"/>
+      <c r="F17" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>157014</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="15"/>
+      <c r="F18" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>105470</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="15"/>
+      <c r="F19" s="8">
         <v>23.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>105457</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="15"/>
+      <c r="F20" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>105456</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="15"/>
+      <c r="F21" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>105468</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="15"/>
+      <c r="F22" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>105458</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="15"/>
+      <c r="F23" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>105471</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="15"/>
+      <c r="F24" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>105435</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="15"/>
+      <c r="F25" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>106053</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="15"/>
+      <c r="F26" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>105062</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="15"/>
+      <c r="F27" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>106032</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="15"/>
+      <c r="F28" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>304309</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="15"/>
+      <c r="F29" s="8">
         <v>8.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>228422</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="15"/>
+      <c r="F30" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>292399</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="15"/>
+      <c r="F31" s="8">
         <v>11.39</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>119916</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="15"/>
+      <c r="F32" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="9">
         <v>132881</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="16"/>
+      <c r="F33" s="11">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>170464</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="15"/>
+      <c r="F34" s="8">
         <v>2.19</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>138538</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="8">
         <v>8.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="79" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="90" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA60F918-9BB8-46A0-AE49-78B32704D16A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B39AB92-EBE3-42D3-9413-F7AA11AAB6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="38">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -88,7 +88,34 @@
     <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
   </si>
   <si>
+    <t>SEGUNDA - AÇOUGUE 25/05/26</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #02 BOVINA</t>
+  </si>
+  <si>
+    <t>CAPA DO CONTRA FILE KG</t>
+  </si>
+  <si>
+    <t>CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>COXÃO MOLE KG</t>
+  </si>
+  <si>
+    <t>#06 AÇOUGUE - #03 SUÍNA</t>
+  </si>
+  <si>
+    <t>COSTELA SUINA KG</t>
+  </si>
+  <si>
+    <t>SUAN SUINA KG</t>
+  </si>
+  <si>
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+  </si>
+  <si>
+    <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
     <t>LINGUIÇA GROSSA SUPER FRANGO KG</t>
@@ -116,7 +143,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,31 +156,57 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -164,6 +217,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -202,22 +261,38 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,328 +598,436 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="85.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>276943</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>15.69</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>104770</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>7.79</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>105842</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>13.49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>294636</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>26.39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>105838</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>9.69</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>104602</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
         <v>16.190000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>105840</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>13.49</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>109597</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>254207</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>108788</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>17.29</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>195365</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="10">
+        <v>239334</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="10">
+        <v>105458</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="12">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="10">
+        <v>105435</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="10">
+        <v>105433</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="12">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="10">
+        <v>106034</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="10">
+        <v>305039</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="12">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="3">
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="6">
         <v>228422</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="D20" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="3">
+      <c r="B21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="6">
         <v>105770</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="D21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9">
         <v>12.19</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="3">
+      <c r="B22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="6">
         <v>105765</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="D22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>11.19</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="3">
+      <c r="B23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="6">
         <v>286228</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="D23" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C18" s="3">
+      <c r="B24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="6">
         <v>170266</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="D24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>1.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - SEGUNDA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D02290-69F0-4013-A268-29E515A2CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821265C0-10EC-487B-8385-F169DF0ED8DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,23 +211,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b/>
       <sz val="7"/>
       <color rgb="FFFFFFFF"/>
@@ -235,15 +218,37 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -293,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -301,34 +306,38 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,571 +644,571 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="41.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>227503</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>9.19</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>276943</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>12.69</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>344990</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>5.29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>158733</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="9">
         <v>12.69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>104770</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>7.89</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>105842</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="10">
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>294636</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="10">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>26.39</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>105838</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="10">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>10.49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>111565</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="10">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>343751</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="10">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>11.9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>105840</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="10">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>13.49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>300409</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="10">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>119927</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="10">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
         <v>11.9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>195365</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="10">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>108771</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="10">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="10">
         <v>105450</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="12">
         <v>41.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="10">
         <v>105468</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="12">
         <v>20.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="10">
         <v>105449</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="11"/>
       <c r="F20" s="12">
         <v>38.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="10">
         <v>106053</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="11"/>
       <c r="F21" s="12">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="10">
         <v>106034</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="12">
         <v>9.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>197181</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="10">
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>26.89</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="10">
         <v>305039</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="12">
         <v>20.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>330507</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>236490</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="10">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>22.89</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>105770</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="10">
+      <c r="E27" s="8"/>
+      <c r="F27" s="9">
         <v>13.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>105765</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="10">
+      <c r="E28" s="8"/>
+      <c r="F28" s="9">
         <v>12.29</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>229897</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="10">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>7.69</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>170464</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="9">
         <v>2.29</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>138538</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <v>8.89</v>
       </c>
     </row>
